--- a/data/trans_orig/P33_1_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26664</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31851</t>
+          <t>32405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18090</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>38109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25775</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48861</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79977</t>
+          <t>80597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>212399</t>
+          <t>211997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>236996</t>
+          <t>236636</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>204976</t>
+          <t>203958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>228650</t>
+          <t>228506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>423236</t>
+          <t>423132</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>458482</t>
+          <t>457477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>28592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35423</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28800</t>
+          <t>30891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>56001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78974</t>
+          <t>81183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116136</t>
+          <t>115592</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129062</t>
+          <t>129828</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>171054</t>
+          <t>167301</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>218024</t>
+          <t>220502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>271790</t>
+          <t>274915</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>357742</t>
+          <t>358723</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>396453</t>
+          <t>394779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>308165</t>
+          <t>308115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>352658</t>
+          <t>350292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679796</t>
+          <t>674932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>734624</t>
+          <t>734757</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20009</t>
+          <t>19854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>23138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46116</t>
+          <t>46259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50505</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78795</t>
+          <t>79140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79018</t>
+          <t>77823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114880</t>
+          <t>115126</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259053</t>
+          <t>259821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>284440</t>
+          <t>285577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247459</t>
+          <t>248308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277919</t>
+          <t>278540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>518305</t>
+          <t>518508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>555510</t>
+          <t>555730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30159</t>
+          <t>29304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48032</t>
+          <t>47401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75674</t>
+          <t>74028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81290</t>
+          <t>81913</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120085</t>
+          <t>121112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>288491</t>
+          <t>289878</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>314709</t>
+          <t>314899</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>286978</t>
+          <t>287588</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>316662</t>
+          <t>316464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>585014</t>
+          <t>585352</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>625608</t>
+          <t>626545</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20288</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19303</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40182</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27104</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50570</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34282</t>
+          <t>33410</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>58128</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>69540</t>
+          <t>68312</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>100577</t>
+          <t>100515</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139201</t>
+          <t>138556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163799</t>
+          <t>163062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131805</t>
+          <t>131740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158337</t>
+          <t>158541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>278741</t>
+          <t>280091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>313242</t>
+          <t>314480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,71%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>23510</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44604</t>
+          <t>44277</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47230</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74533</t>
+          <t>75717</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76618</t>
+          <t>76180</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112223</t>
+          <t>110055</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>214468</t>
+          <t>212866</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>236976</t>
+          <t>236948</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>196525</t>
+          <t>195633</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>224715</t>
+          <t>223502</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>417379</t>
+          <t>418345</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>455039</t>
+          <t>454256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>31805</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24712</t>
+          <t>24852</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48200</t>
+          <t>48994</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58011</t>
+          <t>58812</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>91735</t>
+          <t>91524</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111640</t>
+          <t>114567</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>153865</t>
+          <t>158257</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>183434</t>
+          <t>181128</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>234695</t>
+          <t>235677</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>490963</t>
+          <t>492980</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>529472</t>
+          <t>529321</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>465373</t>
+          <t>462149</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>509824</t>
+          <t>506839</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>970954</t>
+          <t>968033</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1025585</t>
+          <t>1027350</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37806</t>
+          <t>37867</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65401</t>
+          <t>65594</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>43095</t>
+          <t>42867</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>72879</t>
+          <t>72576</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>86432</t>
+          <t>88822</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>127420</t>
+          <t>129502</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>95835</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>135141</t>
+          <t>135162</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>108180</t>
+          <t>108782</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>150534</t>
+          <t>150546</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>217093</t>
+          <t>216589</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>272073</t>
+          <t>274691</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>537793</t>
+          <t>540919</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>583531</t>
+          <t>583917</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>566786</t>
+          <t>565650</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>614967</t>
+          <t>615970</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1118586</t>
+          <t>1119711</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1184821</t>
+          <t>1185839</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>119005</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>165359</t>
+          <t>163163</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>108510</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>153221</t>
+          <t>153480</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>238714</t>
+          <t>238600</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>305440</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>417884</t>
+          <t>419514</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>498886</t>
+          <t>500762</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>628010</t>
+          <t>630708</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>723669</t>
+          <t>722399</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1074562</t>
+          <t>1073329</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1195232</t>
+          <t>1192458</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2588708</t>
+          <t>2582930</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2674029</t>
+          <t>2674378</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2501367</t>
+          <t>2498276</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2598566</t>
+          <t>2596209</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5118185</t>
+          <t>5112156</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5248700</t>
+          <t>5243770</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>22966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23554</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>42779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48117</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78363</t>
+          <t>76184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71926</t>
+          <t>72347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105758</t>
+          <t>105323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128573</t>
+          <t>127718</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176116</t>
+          <t>172764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200256</t>
+          <t>201282</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>231375</t>
+          <t>232380</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165634</t>
+          <t>165805</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>200775</t>
+          <t>201010</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>373852</t>
+          <t>374778</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>422557</t>
+          <t>420731</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44828</t>
+          <t>44628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25510</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49925</t>
+          <t>51241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51848</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85549</t>
+          <t>86349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89223</t>
+          <t>90198</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125754</t>
+          <t>126910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168445</t>
+          <t>171085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>228204</t>
+          <t>228976</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>287196</t>
+          <t>286738</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>340316</t>
+          <t>340616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>384147</t>
+          <t>382092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>317016</t>
+          <t>315613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>362821</t>
+          <t>362562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>669559</t>
+          <t>668299</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>731984</t>
+          <t>730566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>20658</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43791</t>
+          <t>44545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34656</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>41721</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72023</t>
+          <t>70361</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51291</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80203</t>
+          <t>80985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71205</t>
+          <t>73095</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104298</t>
+          <t>106036</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131466</t>
+          <t>133248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176893</t>
+          <t>174292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207407</t>
+          <t>207277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>240547</t>
+          <t>241457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211539</t>
+          <t>210515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248624</t>
+          <t>246691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429532</t>
+          <t>430706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>478692</t>
+          <t>478998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25539</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21150</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44541</t>
+          <t>45193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85045</t>
+          <t>87052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123299</t>
+          <t>122611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138537</t>
+          <t>137602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177693</t>
+          <t>177805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>233749</t>
+          <t>235213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286080</t>
+          <t>286976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>235540</t>
+          <t>235716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>273537</t>
+          <t>273510</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192740</t>
+          <t>193246</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232629</t>
+          <t>235015</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441847</t>
+          <t>441257</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>497942</t>
+          <t>494714</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>22934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20972</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17177</t>
+          <t>16583</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35938</t>
+          <t>36114</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41950</t>
+          <t>41006</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67080</t>
+          <t>67107</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61601</t>
+          <t>61495</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90309</t>
+          <t>90172</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>110532</t>
+          <t>111473</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>149135</t>
+          <t>151154</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130489</t>
+          <t>131825</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>158365</t>
+          <t>159737</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>117381</t>
+          <t>115820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146671</t>
+          <t>145083</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257684</t>
+          <t>255272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>296724</t>
+          <t>294525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>10095</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20373</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41085</t>
+          <t>40058</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39288</t>
+          <t>41352</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65983</t>
+          <t>66178</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>54679</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82273</t>
+          <t>82341</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>100167</t>
+          <t>100112</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138943</t>
+          <t>140839</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>190217</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>220050</t>
+          <t>217443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>184833</t>
+          <t>184877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214725</t>
+          <t>213509</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>382731</t>
+          <t>385169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>425644</t>
+          <t>426625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37230</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42121</t>
+          <t>42787</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>69955</t>
+          <t>68806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97383</t>
+          <t>94994</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139112</t>
+          <t>136598</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147320</t>
+          <t>149445</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>194908</t>
+          <t>196282</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>258037</t>
+          <t>256416</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>316779</t>
+          <t>318369</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>496013</t>
+          <t>498279</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>539104</t>
+          <t>542101</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>466771</t>
+          <t>468072</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>518003</t>
+          <t>516561</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>980081</t>
+          <t>978369</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1043860</t>
+          <t>1045800</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33335</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>62847</t>
+          <t>62489</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27510</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>52297</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>67375</t>
+          <t>68745</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>105516</t>
+          <t>107121</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>110086</t>
+          <t>110226</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>152496</t>
+          <t>152460</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>153944</t>
+          <t>153182</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>202153</t>
+          <t>204159</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>276135</t>
+          <t>274661</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>340021</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>575262</t>
+          <t>575726</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>623898</t>
+          <t>622140</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>575126</t>
+          <t>575865</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>629671</t>
+          <t>629636</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1168604</t>
+          <t>1167066</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1239680</t>
+          <t>1239015</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>164222</t>
+          <t>166372</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>224925</t>
+          <t>224016</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>154361</t>
+          <t>154515</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>208100</t>
+          <t>208287</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>338076</t>
+          <t>335840</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>418265</t>
+          <t>412757</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>645503</t>
+          <t>642439</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>742186</t>
+          <t>740652</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>916489</t>
+          <t>915501</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1027372</t>
+          <t>1034270</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1588926</t>
+          <t>1588104</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1735899</t>
+          <t>1742073</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2477335</t>
+          <t>2471615</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2580460</t>
+          <t>2581173</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2340558</t>
+          <t>2329295</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2457196</t>
+          <t>2449801</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4842118</t>
+          <t>4851463</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5001553</t>
+          <t>5009745</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>39426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64667</t>
+          <t>66353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97788</t>
+          <t>98712</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73793</t>
+          <t>75551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106997</t>
+          <t>106071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150368</t>
+          <t>148855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195111</t>
+          <t>195600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179682</t>
+          <t>177800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>214591</t>
+          <t>212398</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>163671</t>
+          <t>163123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>198047</t>
+          <t>195555</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>351565</t>
+          <t>351059</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>397624</t>
+          <t>398071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17722</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38196</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>29352</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>32169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57326</t>
+          <t>59156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89200</t>
+          <t>89501</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125583</t>
+          <t>127416</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>152218</t>
+          <t>153106</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>196985</t>
+          <t>196356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252440</t>
+          <t>253347</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>313252</t>
+          <t>311105</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>349000</t>
+          <t>347126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>389185</t>
+          <t>388001</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>306595</t>
+          <t>308138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>353169</t>
+          <t>352301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>666340</t>
+          <t>671110</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>729930</t>
+          <t>731636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16161</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49114</t>
+          <t>49607</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50386</t>
+          <t>50479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81235</t>
+          <t>78642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82689</t>
+          <t>84133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119996</t>
+          <t>122006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>265349</t>
+          <t>265953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289084</t>
+          <t>289332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>245820</t>
+          <t>248424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277760</t>
+          <t>277722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>521355</t>
+          <t>520510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>561124</t>
+          <t>559805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,48%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29997</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34753</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31031</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58148</t>
+          <t>57456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90371</t>
+          <t>91680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125413</t>
+          <t>126015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116096</t>
+          <t>117747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155556</t>
+          <t>155271</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218655</t>
+          <t>218644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269330</t>
+          <t>272645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223924</t>
+          <t>224455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>260212</t>
+          <t>261723</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202150</t>
+          <t>201919</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241092</t>
+          <t>241605</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>438330</t>
+          <t>436389</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>490752</t>
+          <t>492174</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22198</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186000</t>
+          <t>186391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201012</t>
+          <t>202026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>190514</t>
+          <t>190244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207074</t>
+          <t>207189</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>383429</t>
+          <t>381857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>405883</t>
+          <t>404512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21103</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31517</t>
+          <t>31472</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29883</t>
+          <t>31205</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53012</t>
+          <t>55594</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59988</t>
+          <t>60814</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88375</t>
+          <t>91462</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97503</t>
+          <t>96321</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>136226</t>
+          <t>136554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>196935</t>
+          <t>196611</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>222809</t>
+          <t>222179</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>174172</t>
+          <t>171026</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204922</t>
+          <t>203275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>377580</t>
+          <t>377726</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>417536</t>
+          <t>418810</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47598</t>
+          <t>47857</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>79908</t>
+          <t>79063</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44156</t>
+          <t>45480</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75088</t>
+          <t>77141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>101126</t>
+          <t>100745</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>143412</t>
+          <t>143925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94827</t>
+          <t>95492</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>135353</t>
+          <t>136467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124577</t>
+          <t>126993</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>172925</t>
+          <t>175234</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>236744</t>
+          <t>234909</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296244</t>
+          <t>295711</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>450532</t>
+          <t>452585</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>498889</t>
+          <t>500156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>456250</t>
+          <t>454279</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>505347</t>
+          <t>504693</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>922957</t>
+          <t>921821</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>991570</t>
+          <t>990277</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31658</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>57279</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>14149</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35498</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>52522</t>
+          <t>50325</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85057</t>
+          <t>84034</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>87182</t>
+          <t>84405</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>124898</t>
+          <t>124235</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>121965</t>
+          <t>120653</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>166873</t>
+          <t>167805</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>215830</t>
+          <t>217605</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>276582</t>
+          <t>276166</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>609122</t>
+          <t>608511</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>651882</t>
+          <t>652810</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>632661</t>
+          <t>629364</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>681719</t>
+          <t>679922</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1257063</t>
+          <t>1257997</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1323839</t>
+          <t>1321584</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>158712</t>
+          <t>159493</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>211330</t>
+          <t>214797</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>139413</t>
+          <t>136422</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>191263</t>
+          <t>188581</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>308090</t>
+          <t>309390</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>381986</t>
+          <t>385627</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>552865</t>
+          <t>555448</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>646236</t>
+          <t>647897</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>789920</t>
+          <t>791115</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>898693</t>
+          <t>894661</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1376248</t>
+          <t>1377849</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1510783</t>
+          <t>1515451</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2552237</t>
+          <t>2552675</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2652505</t>
+          <t>2658807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2468587</t>
+          <t>2467351</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2581803</t>
+          <t>2578401</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5053561</t>
+          <t>5045986</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5198847</t>
+          <t>5198786</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>23049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72076</t>
+          <t>72036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108767</t>
+          <t>107606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82401</t>
+          <t>82594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109347</t>
+          <t>108659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161263</t>
+          <t>163294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204287</t>
+          <t>206585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>194533</t>
+          <t>195838</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>232419</t>
+          <t>232916</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>173617</t>
+          <t>173594</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>200990</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>382172</t>
+          <t>380013</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>427435</t>
+          <t>425499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37034</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29420</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52057</t>
+          <t>54473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84584</t>
+          <t>85592</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129303</t>
+          <t>129075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95735</t>
+          <t>95256</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125077</t>
+          <t>126694</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>186194</t>
+          <t>188982</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242508</t>
+          <t>241612</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>279926</t>
+          <t>280408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>327052</t>
+          <t>325410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>289539</t>
+          <t>288976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>321816</t>
+          <t>321396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>581524</t>
+          <t>581425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>641057</t>
+          <t>637920</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,69%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20346</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64221</t>
+          <t>62479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92359</t>
+          <t>92531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88576</t>
+          <t>87303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117471</t>
+          <t>115304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159094</t>
+          <t>158972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198121</t>
+          <t>197598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214931</t>
+          <t>215587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>244254</t>
+          <t>246464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>220589</t>
+          <t>222131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>249984</t>
+          <t>251039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>446763</t>
+          <t>448155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>487785</t>
+          <t>488707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,13%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24803</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14306</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>31253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59316</t>
+          <t>60829</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94201</t>
+          <t>97002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75071</t>
+          <t>77251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>159114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>144584</t>
+          <t>141126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>237938</t>
+          <t>232478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>206577</t>
+          <t>204675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242800</t>
+          <t>240862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>280079</t>
+          <t>278715</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>374041</t>
+          <t>367960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>503237</t>
+          <t>505951</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>601571</t>
+          <t>603489</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,47 +15612,47 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1138</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51381</t>
+          <t>51425</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71913</t>
+          <t>72537</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>83017</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101949</t>
+          <t>101665</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140151</t>
+          <t>139064</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170156</t>
+          <t>168326</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106829</t>
+          <t>106205</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127361</t>
+          <t>127317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105433</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124261</t>
+          <t>123666</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>215738</t>
+          <t>217912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>245865</t>
+          <t>246099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>327</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>857</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50951</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74015</t>
+          <t>73119</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77839</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101499</t>
+          <t>100707</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>133375</t>
+          <t>132754</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>166825</t>
+          <t>166117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>194730</t>
+          <t>195366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>217733</t>
+          <t>217449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153920</t>
+          <t>154725</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>177656</t>
+          <t>178523</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>357715</t>
+          <t>358570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>390930</t>
+          <t>392087</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>33083</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>160497</t>
+          <t>159223</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>215361</t>
+          <t>211244</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>284071</t>
+          <t>282531</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>641082</t>
+          <t>630350</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>461473</t>
+          <t>459873</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>909066</t>
+          <t>922483</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>398999</t>
+          <t>402778</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>453872</t>
+          <t>455736</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>197265</t>
+          <t>208317</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>544324</t>
+          <t>546017</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>541304</t>
+          <t>531127</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>981193</t>
+          <t>983527</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,97%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>21649</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>31426</t>
+          <t>36451</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>107912</t>
+          <t>109942</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>77586</t>
+          <t>77300</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>106778</t>
+          <t>107615</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>103570</t>
+          <t>102484</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>204116</t>
+          <t>203746</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>815951</t>
+          <t>814189</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>895839</t>
+          <t>889794</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>596701</t>
+          <t>598248</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>628918</t>
+          <t>628514</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1424489</t>
+          <t>1422396</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1531373</t>
+          <t>1530725</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>32721</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>59419</t>
+          <t>60908</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>65634</t>
+          <t>64415</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>98202</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,47 +17451,47 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>127251</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>106684</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>150559</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>127251</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>106860</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>150318</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>555872</t>
+          <t>555649</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>804671</t>
+          <t>814346</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>957287</t>
+          <t>964315</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1572170</t>
+          <t>1607245</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1651941</t>
+          <t>1636959</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2309525</t>
+          <t>2357000</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2503236</t>
+          <t>2493003</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2771638</t>
+          <t>2764034</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1916101</t>
+          <t>1893941</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2514675</t>
+          <t>2510660</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4492493</t>
+          <t>4450941</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5138820</t>
+          <t>5157772</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
